--- a/data/trans_orig/P79A3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A3_2023-Clase-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>711</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>711</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>738</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>704</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19273</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
